--- a/Main/AUT_EEC_results/AUT_EEC_epem_a0.10_b0.10_chibar15_Q4_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_epem_a0.10_b0.10_chibar15_Q4_LO.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.00168705284445172</v>
+        <v>0.001645773049436172</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00168705284445172</v>
+        <v>0.001645773049436172</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001232036142234813</v>
+        <v>0.001387667043749606</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.001658227130271625</v>
+        <v>0.001619715497799252</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001658227130271625</v>
+        <v>0.001619715497799252</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001260626543176052</v>
+        <v>0.001432286313025068</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.001661072744856747</v>
+        <v>0.001621585055605317</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001661072744856747</v>
+        <v>0.001621585055605317</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001236249700859876</v>
+        <v>0.001412132997222609</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.001658967628275908</v>
+        <v>0.001617240148581562</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001658967628275908</v>
+        <v>0.001617240148581562</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001225800416236131</v>
+        <v>0.001399702800844563</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.001645531876885487</v>
+        <v>0.001601110049201765</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001645531876885487</v>
+        <v>0.001601110049201765</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001216874856710009</v>
+        <v>0.00139236508539142</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.001635316137819246</v>
+        <v>0.001587808730952822</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001635316137819246</v>
+        <v>0.001587808730952822</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001207736324845429</v>
+        <v>0.001385962307287793</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.001616404627265228</v>
+        <v>0.001565743097496083</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001616404627265228</v>
+        <v>0.001565743097496083</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001198089319901735</v>
+        <v>0.001379856327936487</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.001595689900324218</v>
+        <v>0.001541854015541732</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001595689900324218</v>
+        <v>0.001541854015541732</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001187081662942987</v>
+        <v>0.00137178406976339</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.001573622340686975</v>
+        <v>0.001516739350309209</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001573622340686975</v>
+        <v>0.001516739350309209</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001173537605263215</v>
+        <v>0.001359786362163388</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.001551204810603653</v>
+        <v>0.001491705036905802</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001551204810603653</v>
+        <v>0.001491705036905802</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001156136140196931</v>
+        <v>0.001342655671219343</v>
       </c>
     </row>
     <row r="12">
@@ -595,13 +595,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.001529721295806102</v>
+        <v>0.001467716605016339</v>
       </c>
       <c r="C12" t="n">
-        <v>0.001529721295806102</v>
+        <v>0.001467716605016339</v>
       </c>
       <c r="D12" t="n">
-        <v>0.00113541241816685</v>
+        <v>0.001320116442658889</v>
       </c>
     </row>
     <row r="13">
@@ -609,13 +609,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.00151008534433355</v>
+        <v>0.001446133902773964</v>
       </c>
       <c r="C13" t="n">
-        <v>0.00151008534433355</v>
+        <v>0.001446133902773964</v>
       </c>
       <c r="D13" t="n">
-        <v>0.001112667437211489</v>
+        <v>0.001292699975396614</v>
       </c>
     </row>
     <row r="14">
@@ -623,13 +623,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.00149315548578384</v>
+        <v>0.001427705776091632</v>
       </c>
       <c r="C14" t="n">
-        <v>0.00149315548578384</v>
+        <v>0.001427705776091632</v>
       </c>
       <c r="D14" t="n">
-        <v>0.001087090337498216</v>
+        <v>0.001261077512393278</v>
       </c>
     </row>
     <row r="15">
@@ -637,13 +637,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.001479246409218092</v>
+        <v>0.001412739710619234</v>
       </c>
       <c r="C15" t="n">
-        <v>0.001479246409218092</v>
+        <v>0.001412739710619234</v>
       </c>
       <c r="D15" t="n">
-        <v>0.00105988244374765</v>
+        <v>0.001225867921724395</v>
       </c>
     </row>
     <row r="16">
@@ -651,13 +651,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.001468525549067262</v>
+        <v>0.001401382962892778</v>
       </c>
       <c r="C16" t="n">
-        <v>0.001468525549067262</v>
+        <v>0.001401382962892778</v>
       </c>
       <c r="D16" t="n">
-        <v>0.001031186495547273</v>
+        <v>0.001187381920793723</v>
       </c>
     </row>
     <row r="17">
@@ -665,13 +665,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.001461245644828004</v>
+        <v>0.00139386139491145</v>
       </c>
       <c r="C17" t="n">
-        <v>0.001461245644828004</v>
+        <v>0.00139386139491145</v>
       </c>
       <c r="D17" t="n">
-        <v>0.001001897482518947</v>
+        <v>0.001146288983950183</v>
       </c>
     </row>
     <row r="18">
@@ -679,13 +679,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.001457875683966925</v>
+        <v>0.001390613180077804</v>
       </c>
       <c r="C18" t="n">
-        <v>0.001457875683966925</v>
+        <v>0.001390613180077804</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0009720265021325824</v>
+        <v>0.001103210269314835</v>
       </c>
     </row>
     <row r="19">
@@ -693,13 +693,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.001458995346022773</v>
+        <v>0.001392181453947084</v>
       </c>
       <c r="C19" t="n">
-        <v>0.001458995346022773</v>
+        <v>0.001392181453947084</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0009434073885263687</v>
+        <v>0.001059908492963082</v>
       </c>
     </row>
     <row r="20">
@@ -707,13 +707,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.001465179831907518</v>
+        <v>0.00139910297477134</v>
       </c>
       <c r="C20" t="n">
-        <v>0.001465179831907518</v>
+        <v>0.00139910297477134</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0009149261322366403</v>
+        <v>0.001019580862435113</v>
       </c>
     </row>
     <row r="21">
@@ -721,13 +721,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.001476803668741479</v>
+        <v>0.00141169900034612</v>
       </c>
       <c r="C21" t="n">
-        <v>0.001476803668741479</v>
+        <v>0.00141169900034612</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0008889328492354857</v>
+        <v>0.0009795453687467036</v>
       </c>
     </row>
     <row r="22">
@@ -735,13 +735,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.001494429774506619</v>
+        <v>0.001430513210611866</v>
       </c>
       <c r="C22" t="n">
-        <v>0.001494429774506619</v>
+        <v>0.001430513210611866</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0008645960733322538</v>
+        <v>0.000942622764375147</v>
       </c>
     </row>
     <row r="23">
@@ -749,13 +749,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.001518270630546451</v>
+        <v>0.001455723408266193</v>
       </c>
       <c r="C23" t="n">
-        <v>0.001518270630546451</v>
+        <v>0.001455723408266193</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0008420182719848983</v>
+        <v>0.0009093605754925338</v>
       </c>
     </row>
     <row r="24">
@@ -763,13 +763,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.001548553868191797</v>
+        <v>0.001483856742758862</v>
       </c>
       <c r="C24" t="n">
-        <v>0.001548553868191797</v>
+        <v>0.001483856742758862</v>
       </c>
       <c r="D24" t="n">
-        <v>0.000825157852373629</v>
+        <v>0.0008780621208627273</v>
       </c>
     </row>
     <row r="25">
@@ -777,13 +777,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.001580709006891942</v>
+        <v>0.001521252465686451</v>
       </c>
       <c r="C25" t="n">
-        <v>0.001580709006891942</v>
+        <v>0.001521252465686451</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0008112739475216195</v>
+        <v>0.0008530891135213413</v>
       </c>
     </row>
     <row r="26">
@@ -791,13 +791,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.001623759270029235</v>
+        <v>0.001566003260879758</v>
       </c>
       <c r="C26" t="n">
-        <v>0.001623759270029235</v>
+        <v>0.001566003260879758</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0007992918869648134</v>
+        <v>0.0008322641322532462</v>
       </c>
     </row>
     <row r="27">
@@ -805,13 +805,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.001674488634104374</v>
+        <v>0.001618398800815528</v>
       </c>
       <c r="C27" t="n">
-        <v>0.001674488634104374</v>
+        <v>0.001618398800815528</v>
       </c>
       <c r="D27" t="n">
-        <v>0.000792674596565151</v>
+        <v>0.0008219619715238816</v>
       </c>
     </row>
     <row r="28">
@@ -819,13 +819,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.001733148101469821</v>
+        <v>0.001678735225977125</v>
       </c>
       <c r="C28" t="n">
-        <v>0.001733148101469821</v>
+        <v>0.001678735225977125</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0007895344726089166</v>
+        <v>0.0008155530248153748</v>
       </c>
     </row>
     <row r="29">
@@ -833,13 +833,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.001799964888324225</v>
+        <v>0.001747201497970745</v>
       </c>
       <c r="C29" t="n">
-        <v>0.001799964888324225</v>
+        <v>0.001747201497970745</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0007906026425797617</v>
+        <v>0.0008140938487836602</v>
       </c>
     </row>
     <row r="30">
@@ -847,13 +847,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.001875070410353186</v>
+        <v>0.001823914127007914</v>
       </c>
       <c r="C30" t="n">
-        <v>0.001875070410353186</v>
+        <v>0.001823914127007914</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0007956545626573422</v>
+        <v>0.0008172923912660139</v>
       </c>
     </row>
     <row r="31">
@@ -861,13 +861,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.001958553647885253</v>
+        <v>0.001908939226517721</v>
       </c>
       <c r="C31" t="n">
-        <v>0.001958553647885253</v>
+        <v>0.001908939226517721</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0008036336709253202</v>
+        <v>0.0008257168465548034</v>
       </c>
     </row>
   </sheetData>
